--- a/wiki/comparisons/출하현황_납품처별_월별분석_2026.xlsx
+++ b/wiki/comparisons/출하현황_납품처별_월별분석_2026.xlsx
@@ -673,7 +673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P73"/>
+  <dimension ref="A1:P77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -817,7 +817,7 @@
         <v>107</v>
       </c>
       <c r="K3" s="26" t="n">
-        <v>0</v>
+        <v>257</v>
       </c>
       <c r="L3" s="26" t="n">
         <v>0</v>
@@ -833,7 +833,7 @@
         <v/>
       </c>
       <c r="P3" s="28">
-        <f>O3/O$73</f>
+        <f>O3/O$77</f>
         <v/>
       </c>
     </row>
@@ -887,7 +887,7 @@
         <v/>
       </c>
       <c r="P4" s="28">
-        <f>O4/O$73</f>
+        <f>O4/O$77</f>
         <v/>
       </c>
     </row>
@@ -941,7 +941,7 @@
         <v/>
       </c>
       <c r="P5" s="28">
-        <f>O5/O$73</f>
+        <f>O5/O$77</f>
         <v/>
       </c>
     </row>
@@ -995,7 +995,7 @@
         <v/>
       </c>
       <c r="P6" s="28">
-        <f>O6/O$73</f>
+        <f>O6/O$77</f>
         <v/>
       </c>
     </row>
@@ -1033,7 +1033,7 @@
         <v>16</v>
       </c>
       <c r="K7" s="26" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="L7" s="26" t="n">
         <v>0</v>
@@ -1049,7 +1049,7 @@
         <v/>
       </c>
       <c r="P7" s="28">
-        <f>O7/O$73</f>
+        <f>O7/O$77</f>
         <v/>
       </c>
     </row>
@@ -1087,7 +1087,7 @@
         <v>107</v>
       </c>
       <c r="K8" s="26" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="L8" s="26" t="n">
         <v>0</v>
@@ -1103,7 +1103,7 @@
         <v/>
       </c>
       <c r="P8" s="28">
-        <f>O8/O$73</f>
+        <f>O8/O$77</f>
         <v/>
       </c>
     </row>
@@ -1113,35 +1113,35 @@
       </c>
       <c r="B9" s="25" t="inlineStr">
         <is>
-          <t>연성기공(주)</t>
+          <t>아이티공구</t>
         </is>
       </c>
       <c r="C9" s="26" t="n">
-        <v>7</v>
+        <v>61</v>
       </c>
       <c r="D9" s="26" t="n">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="E9" s="26" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="F9" s="26" t="n">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="G9" s="26" t="n">
-        <v>192</v>
+        <v>118</v>
       </c>
       <c r="H9" s="26" t="n">
-        <v>121</v>
+        <v>13</v>
       </c>
       <c r="I9" s="26" t="n">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="J9" s="26" t="n">
-        <v>23</v>
+        <v>67</v>
       </c>
       <c r="K9" s="26" t="n">
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="L9" s="26" t="n">
         <v>0</v>
@@ -1157,7 +1157,7 @@
         <v/>
       </c>
       <c r="P9" s="28">
-        <f>O9/O$73</f>
+        <f>O9/O$77</f>
         <v/>
       </c>
     </row>
@@ -1167,35 +1167,35 @@
       </c>
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>아신상사</t>
+          <t>영우툴링(창성툴)</t>
         </is>
       </c>
       <c r="C10" s="26" t="n">
-        <v>0</v>
+        <v>159</v>
       </c>
       <c r="D10" s="26" t="n">
-        <v>134</v>
+        <v>72</v>
       </c>
       <c r="E10" s="26" t="n">
-        <v>152</v>
+        <v>34</v>
       </c>
       <c r="F10" s="26" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="G10" s="26" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="H10" s="26" t="n">
-        <v>138</v>
+        <v>57</v>
       </c>
       <c r="I10" s="26" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="J10" s="26" t="n">
-        <v>155</v>
+        <v>40</v>
       </c>
       <c r="K10" s="26" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="L10" s="26" t="n">
         <v>0</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="P10" s="28">
-        <f>O10/O$73</f>
+        <f>O10/O$77</f>
         <v/>
       </c>
     </row>
@@ -1221,32 +1221,32 @@
       </c>
       <c r="B11" s="25" t="inlineStr">
         <is>
-          <t>영우툴링(창성툴)</t>
+          <t>연성기공(주)</t>
         </is>
       </c>
       <c r="C11" s="26" t="n">
-        <v>159</v>
+        <v>7</v>
       </c>
       <c r="D11" s="26" t="n">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="E11" s="26" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="F11" s="26" t="n">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="G11" s="26" t="n">
-        <v>66</v>
+        <v>192</v>
       </c>
       <c r="H11" s="26" t="n">
-        <v>57</v>
+        <v>121</v>
       </c>
       <c r="I11" s="26" t="n">
-        <v>109</v>
+        <v>139</v>
       </c>
       <c r="J11" s="26" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="K11" s="26" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v/>
       </c>
       <c r="P11" s="28">
-        <f>O11/O$73</f>
+        <f>O11/O$77</f>
         <v/>
       </c>
     </row>
@@ -1275,32 +1275,32 @@
       </c>
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>아이티공구</t>
+          <t>아신상사</t>
         </is>
       </c>
       <c r="C12" s="26" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="D12" s="26" t="n">
-        <v>83</v>
+        <v>134</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>43</v>
+        <v>152</v>
       </c>
       <c r="F12" s="26" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="G12" s="26" t="n">
-        <v>118</v>
+        <v>0</v>
       </c>
       <c r="H12" s="26" t="n">
-        <v>13</v>
+        <v>138</v>
       </c>
       <c r="I12" s="26" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="J12" s="26" t="n">
-        <v>67</v>
+        <v>155</v>
       </c>
       <c r="K12" s="26" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
         <v/>
       </c>
       <c r="P12" s="28">
-        <f>O12/O$73</f>
+        <f>O12/O$77</f>
         <v/>
       </c>
     </row>
@@ -1329,35 +1329,35 @@
       </c>
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>유비툴</t>
+          <t>왕삼아공구</t>
         </is>
       </c>
       <c r="C13" s="26" t="n">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="D13" s="26" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="E13" s="26" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="F13" s="26" t="n">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="G13" s="26" t="n">
-        <v>182</v>
+        <v>156</v>
       </c>
       <c r="H13" s="26" t="n">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="I13" s="26" t="n">
         <v>15</v>
       </c>
       <c r="J13" s="26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" s="26" t="n">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="L13" s="26" t="n">
         <v>0</v>
@@ -1373,7 +1373,7 @@
         <v/>
       </c>
       <c r="P13" s="28">
-        <f>O13/O$73</f>
+        <f>O13/O$77</f>
         <v/>
       </c>
     </row>
@@ -1383,35 +1383,35 @@
       </c>
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>(주)공화공구</t>
+          <t>유비툴</t>
         </is>
       </c>
       <c r="C14" s="26" t="n">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="D14" s="26" t="n">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="E14" s="26" t="n">
-        <v>11</v>
+        <v>53</v>
       </c>
       <c r="F14" s="26" t="n">
-        <v>3</v>
+        <v>53</v>
       </c>
       <c r="G14" s="26" t="n">
-        <v>34</v>
+        <v>182</v>
       </c>
       <c r="H14" s="26" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I14" s="26" t="n">
-        <v>90</v>
+        <v>15</v>
       </c>
       <c r="J14" s="26" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="K14" s="26" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="L14" s="26" t="n">
         <v>0</v>
@@ -1427,7 +1427,7 @@
         <v/>
       </c>
       <c r="P14" s="28">
-        <f>O14/O$73</f>
+        <f>O14/O$77</f>
         <v/>
       </c>
     </row>
@@ -1465,7 +1465,7 @@
         <v>67</v>
       </c>
       <c r="K15" s="26" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L15" s="26" t="n">
         <v>0</v>
@@ -1481,7 +1481,7 @@
         <v/>
       </c>
       <c r="P15" s="28">
-        <f>O15/O$73</f>
+        <f>O15/O$77</f>
         <v/>
       </c>
     </row>
@@ -1491,35 +1491,35 @@
       </c>
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>알제이코리아</t>
+          <t>(주)공화공구</t>
         </is>
       </c>
       <c r="C16" s="26" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D16" s="26" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="E16" s="26" t="n">
-        <v>70</v>
+        <v>11</v>
       </c>
       <c r="F16" s="26" t="n">
-        <v>75</v>
+        <v>3</v>
       </c>
       <c r="G16" s="26" t="n">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="H16" s="26" t="n">
-        <v>58</v>
+        <v>17</v>
       </c>
       <c r="I16" s="26" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="J16" s="26" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="K16" s="26" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L16" s="26" t="n">
         <v>0</v>
@@ -1535,7 +1535,7 @@
         <v/>
       </c>
       <c r="P16" s="28">
-        <f>O16/O$73</f>
+        <f>O16/O$77</f>
         <v/>
       </c>
     </row>
@@ -1573,7 +1573,7 @@
         <v>59</v>
       </c>
       <c r="K17" s="26" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L17" s="26" t="n">
         <v>0</v>
@@ -1589,7 +1589,7 @@
         <v/>
       </c>
       <c r="P17" s="28">
-        <f>O17/O$73</f>
+        <f>O17/O$77</f>
         <v/>
       </c>
     </row>
@@ -1599,35 +1599,35 @@
       </c>
       <c r="B18" s="25" t="inlineStr">
         <is>
-          <t>왕삼아공구</t>
+          <t>알제이코리아</t>
         </is>
       </c>
       <c r="C18" s="26" t="n">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="D18" s="26" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E18" s="26" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="F18" s="26" t="n">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="G18" s="26" t="n">
-        <v>156</v>
+        <v>8</v>
       </c>
       <c r="H18" s="26" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="I18" s="26" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="J18" s="26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" s="26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L18" s="26" t="n">
         <v>0</v>
@@ -1643,7 +1643,7 @@
         <v/>
       </c>
       <c r="P18" s="28">
-        <f>O18/O$73</f>
+        <f>O18/O$77</f>
         <v/>
       </c>
     </row>
@@ -1697,7 +1697,7 @@
         <v/>
       </c>
       <c r="P19" s="28">
-        <f>O19/O$73</f>
+        <f>O19/O$77</f>
         <v/>
       </c>
     </row>
@@ -1751,7 +1751,7 @@
         <v/>
       </c>
       <c r="P20" s="28">
-        <f>O20/O$73</f>
+        <f>O20/O$77</f>
         <v/>
       </c>
     </row>
@@ -1761,14 +1761,14 @@
       </c>
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>(주)세종종합상사(미산동)</t>
+          <t>유진상사(문래)</t>
         </is>
       </c>
       <c r="C21" s="26" t="n">
         <v>0</v>
       </c>
       <c r="D21" s="26" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E21" s="26" t="n">
         <v>0</v>
@@ -1777,19 +1777,19 @@
         <v>0</v>
       </c>
       <c r="G21" s="26" t="n">
-        <v>64</v>
+        <v>19</v>
       </c>
       <c r="H21" s="26" t="n">
         <v>0</v>
       </c>
       <c r="I21" s="26" t="n">
-        <v>134</v>
+        <v>1</v>
       </c>
       <c r="J21" s="26" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K21" s="26" t="n">
-        <v>0</v>
+        <v>195</v>
       </c>
       <c r="L21" s="26" t="n">
         <v>0</v>
@@ -1805,7 +1805,7 @@
         <v/>
       </c>
       <c r="P21" s="28">
-        <f>O21/O$73</f>
+        <f>O21/O$77</f>
         <v/>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
         <v>0</v>
       </c>
       <c r="K22" s="26" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="L22" s="26" t="n">
         <v>0</v>
@@ -1859,7 +1859,7 @@
         <v/>
       </c>
       <c r="P22" s="28">
-        <f>O22/O$73</f>
+        <f>O22/O$77</f>
         <v/>
       </c>
     </row>
@@ -1869,35 +1869,35 @@
       </c>
       <c r="B23" s="25" t="inlineStr">
         <is>
-          <t>핫몰드엔지니어링주식회사-코고툴(재연마)</t>
+          <t>서림툴링</t>
         </is>
       </c>
       <c r="C23" s="26" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D23" s="26" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="E23" s="26" t="n">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="F23" s="26" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G23" s="26" t="n">
         <v>0</v>
       </c>
       <c r="H23" s="26" t="n">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="I23" s="26" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="J23" s="26" t="n">
-        <v>57</v>
+        <v>18</v>
       </c>
       <c r="K23" s="26" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="L23" s="26" t="n">
         <v>0</v>
@@ -1913,7 +1913,7 @@
         <v/>
       </c>
       <c r="P23" s="28">
-        <f>O23/O$73</f>
+        <f>O23/O$77</f>
         <v/>
       </c>
     </row>
@@ -1923,32 +1923,32 @@
       </c>
       <c r="B24" s="25" t="inlineStr">
         <is>
-          <t>서림툴링</t>
+          <t>(주)세종종합상사(미산동)</t>
         </is>
       </c>
       <c r="C24" s="26" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D24" s="26" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="E24" s="26" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F24" s="26" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="G24" s="26" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="H24" s="26" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="I24" s="26" t="n">
-        <v>21</v>
+        <v>134</v>
       </c>
       <c r="J24" s="26" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K24" s="26" t="n">
         <v>0</v>
@@ -1967,7 +1967,7 @@
         <v/>
       </c>
       <c r="P24" s="28">
-        <f>O24/O$73</f>
+        <f>O24/O$77</f>
         <v/>
       </c>
     </row>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>동명ENG-코고툴(재연마)</t>
+          <t>핫몰드엔지니어링주식회사-코고툴(재연마)</t>
         </is>
       </c>
       <c r="C25" s="26" t="n">
@@ -1987,7 +1987,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="26" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="F25" s="26" t="n">
         <v>0</v>
@@ -1996,13 +1996,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="26" t="n">
-        <v>84</v>
+        <v>52</v>
       </c>
       <c r="I25" s="26" t="n">
         <v>0</v>
       </c>
       <c r="J25" s="26" t="n">
-        <v>86</v>
+        <v>57</v>
       </c>
       <c r="K25" s="26" t="n">
         <v>0</v>
@@ -2021,7 +2021,7 @@
         <v/>
       </c>
       <c r="P25" s="28">
-        <f>O25/O$73</f>
+        <f>O25/O$77</f>
         <v/>
       </c>
     </row>
@@ -2031,7 +2031,7 @@
       </c>
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>지니툴(구로)_코고툴</t>
+          <t>동명ENG-코고툴(재연마)</t>
         </is>
       </c>
       <c r="C26" s="26" t="n">
@@ -2050,13 +2050,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="26" t="n">
-        <v>30</v>
+        <v>84</v>
       </c>
       <c r="I26" s="26" t="n">
         <v>0</v>
       </c>
       <c r="J26" s="26" t="n">
-        <v>116</v>
+        <v>86</v>
       </c>
       <c r="K26" s="26" t="n">
         <v>0</v>
@@ -2075,7 +2075,7 @@
         <v/>
       </c>
       <c r="P26" s="28">
-        <f>O26/O$73</f>
+        <f>O26/O$77</f>
         <v/>
       </c>
     </row>
@@ -2085,32 +2085,32 @@
       </c>
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>대우툴링</t>
+          <t>지니툴(구로)_코고툴</t>
         </is>
       </c>
       <c r="C27" s="26" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="D27" s="26" t="n">
         <v>0</v>
       </c>
       <c r="E27" s="26" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F27" s="26" t="n">
         <v>0</v>
       </c>
       <c r="G27" s="26" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H27" s="26" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="I27" s="26" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J27" s="26" t="n">
-        <v>9</v>
+        <v>116</v>
       </c>
       <c r="K27" s="26" t="n">
         <v>0</v>
@@ -2129,7 +2129,7 @@
         <v/>
       </c>
       <c r="P27" s="28">
-        <f>O27/O$73</f>
+        <f>O27/O$77</f>
         <v/>
       </c>
     </row>
@@ -2139,26 +2139,26 @@
       </c>
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>이엠티(EMT)</t>
+          <t>영창툴링</t>
         </is>
       </c>
       <c r="C28" s="26" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D28" s="26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E28" s="26" t="n">
-        <v>104</v>
+        <v>17</v>
       </c>
       <c r="F28" s="26" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="G28" s="26" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="H28" s="26" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I28" s="26" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="K28" s="26" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L28" s="26" t="n">
         <v>0</v>
@@ -2183,7 +2183,7 @@
         <v/>
       </c>
       <c r="P28" s="28">
-        <f>O28/O$73</f>
+        <f>O28/O$77</f>
         <v/>
       </c>
     </row>
@@ -2193,32 +2193,32 @@
       </c>
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>영창툴링</t>
+          <t>대우툴링</t>
         </is>
       </c>
       <c r="C29" s="26" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="D29" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="26" t="n">
         <v>10</v>
       </c>
-      <c r="E29" s="26" t="n">
-        <v>17</v>
-      </c>
       <c r="F29" s="26" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G29" s="26" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H29" s="26" t="n">
+        <v>20</v>
+      </c>
+      <c r="I29" s="26" t="n">
         <v>10</v>
       </c>
-      <c r="I29" s="26" t="n">
-        <v>0</v>
-      </c>
       <c r="J29" s="26" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K29" s="26" t="n">
         <v>0</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="P29" s="28">
-        <f>O29/O$73</f>
+        <f>O29/O$77</f>
         <v/>
       </c>
     </row>
@@ -2247,26 +2247,26 @@
       </c>
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>다영툴링</t>
+          <t>이엠티(EMT)</t>
         </is>
       </c>
       <c r="C30" s="26" t="n">
         <v>0</v>
       </c>
       <c r="D30" s="26" t="n">
-        <v>82</v>
+        <v>9</v>
       </c>
       <c r="E30" s="26" t="n">
-        <v>17</v>
+        <v>104</v>
       </c>
       <c r="F30" s="26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G30" s="26" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H30" s="26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I30" s="26" t="n">
         <v>0</v>
@@ -2291,7 +2291,7 @@
         <v/>
       </c>
       <c r="P30" s="28">
-        <f>O30/O$73</f>
+        <f>O30/O$77</f>
         <v/>
       </c>
     </row>
@@ -2329,7 +2329,7 @@
         <v>5</v>
       </c>
       <c r="K31" s="26" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L31" s="26" t="n">
         <v>0</v>
@@ -2345,7 +2345,7 @@
         <v/>
       </c>
       <c r="P31" s="28">
-        <f>O31/O$73</f>
+        <f>O31/O$77</f>
         <v/>
       </c>
     </row>
@@ -2355,17 +2355,17 @@
       </c>
       <c r="B32" s="25" t="inlineStr">
         <is>
-          <t>스마트툴스</t>
+          <t>다영툴링</t>
         </is>
       </c>
       <c r="C32" s="26" t="n">
         <v>0</v>
       </c>
       <c r="D32" s="26" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="E32" s="26" t="n">
-        <v>95</v>
+        <v>17</v>
       </c>
       <c r="F32" s="26" t="n">
         <v>0</v>
@@ -2399,7 +2399,7 @@
         <v/>
       </c>
       <c r="P32" s="28">
-        <f>O32/O$73</f>
+        <f>O32/O$77</f>
         <v/>
       </c>
     </row>
@@ -2409,17 +2409,17 @@
       </c>
       <c r="B33" s="25" t="inlineStr">
         <is>
-          <t>E-tech(이테크)</t>
+          <t>스마트툴스</t>
         </is>
       </c>
       <c r="C33" s="26" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D33" s="26" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="E33" s="26" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="F33" s="26" t="n">
         <v>0</v>
@@ -2431,7 +2431,7 @@
         <v>0</v>
       </c>
       <c r="I33" s="26" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J33" s="26" t="n">
         <v>0</v>
@@ -2453,7 +2453,7 @@
         <v/>
       </c>
       <c r="P33" s="28">
-        <f>O33/O$73</f>
+        <f>O33/O$77</f>
         <v/>
       </c>
     </row>
@@ -2463,14 +2463,14 @@
       </c>
       <c r="B34" s="25" t="inlineStr">
         <is>
-          <t>(주)정원테크</t>
+          <t>E-tech(이테크)</t>
         </is>
       </c>
       <c r="C34" s="26" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D34" s="26" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E34" s="26" t="n">
         <v>0</v>
@@ -2479,16 +2479,16 @@
         <v>0</v>
       </c>
       <c r="G34" s="26" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H34" s="26" t="n">
         <v>0</v>
       </c>
       <c r="I34" s="26" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J34" s="26" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K34" s="26" t="n">
         <v>0</v>
@@ -2507,7 +2507,7 @@
         <v/>
       </c>
       <c r="P34" s="28">
-        <f>O34/O$73</f>
+        <f>O34/O$77</f>
         <v/>
       </c>
     </row>
@@ -2517,32 +2517,32 @@
       </c>
       <c r="B35" s="25" t="inlineStr">
         <is>
-          <t>광진테크</t>
+          <t>(주)정원테크</t>
         </is>
       </c>
       <c r="C35" s="26" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="D35" s="26" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E35" s="26" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F35" s="26" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G35" s="26" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H35" s="26" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I35" s="26" t="n">
         <v>0</v>
       </c>
       <c r="J35" s="26" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="K35" s="26" t="n">
         <v>0</v>
@@ -2561,7 +2561,7 @@
         <v/>
       </c>
       <c r="P35" s="28">
-        <f>O35/O$73</f>
+        <f>O35/O$77</f>
         <v/>
       </c>
     </row>
@@ -2571,14 +2571,14 @@
       </c>
       <c r="B36" s="25" t="inlineStr">
         <is>
-          <t>뉴툴(New tool)</t>
+          <t>(주)일등정밀공구(안산)</t>
         </is>
       </c>
       <c r="C36" s="26" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="D36" s="26" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E36" s="26" t="n">
         <v>0</v>
@@ -2587,19 +2587,19 @@
         <v>0</v>
       </c>
       <c r="G36" s="26" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H36" s="26" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I36" s="26" t="n">
         <v>0</v>
       </c>
       <c r="J36" s="26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K36" s="26" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="L36" s="26" t="n">
         <v>0</v>
@@ -2615,7 +2615,7 @@
         <v/>
       </c>
       <c r="P36" s="28">
-        <f>O36/O$73</f>
+        <f>O36/O$77</f>
         <v/>
       </c>
     </row>
@@ -2625,35 +2625,35 @@
       </c>
       <c r="B37" s="25" t="inlineStr">
         <is>
-          <t>(주)전진공구</t>
+          <t>광진테크</t>
         </is>
       </c>
       <c r="C37" s="26" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="D37" s="26" t="n">
         <v>0</v>
       </c>
       <c r="E37" s="26" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F37" s="26" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G37" s="26" t="n">
         <v>0</v>
       </c>
       <c r="H37" s="26" t="n">
-        <v>53</v>
+        <v>8</v>
       </c>
       <c r="I37" s="26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J37" s="26" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="K37" s="26" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L37" s="26" t="n">
         <v>0</v>
@@ -2669,7 +2669,7 @@
         <v/>
       </c>
       <c r="P37" s="28">
-        <f>O37/O$73</f>
+        <f>O37/O$77</f>
         <v/>
       </c>
     </row>
@@ -2679,14 +2679,14 @@
       </c>
       <c r="B38" s="25" t="inlineStr">
         <is>
-          <t>(주)일등정밀공구(안산)</t>
+          <t>뉴툴(New tool)</t>
         </is>
       </c>
       <c r="C38" s="26" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="D38" s="26" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E38" s="26" t="n">
         <v>0</v>
@@ -2695,16 +2695,16 @@
         <v>0</v>
       </c>
       <c r="G38" s="26" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="H38" s="26" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I38" s="26" t="n">
         <v>0</v>
       </c>
       <c r="J38" s="26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K38" s="26" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
         <v/>
       </c>
       <c r="P38" s="28">
-        <f>O38/O$73</f>
+        <f>O38/O$77</f>
         <v/>
       </c>
     </row>
@@ -2733,29 +2733,29 @@
       </c>
       <c r="B39" s="25" t="inlineStr">
         <is>
-          <t>맨날툴이야</t>
+          <t>(주)전진공구</t>
         </is>
       </c>
       <c r="C39" s="26" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D39" s="26" t="n">
         <v>0</v>
       </c>
       <c r="E39" s="26" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F39" s="26" t="n">
         <v>0</v>
       </c>
       <c r="G39" s="26" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H39" s="26" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="I39" s="26" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J39" s="26" t="n">
         <v>14</v>
@@ -2777,7 +2777,7 @@
         <v/>
       </c>
       <c r="P39" s="28">
-        <f>O39/O$73</f>
+        <f>O39/O$77</f>
         <v/>
       </c>
     </row>
@@ -2787,32 +2787,32 @@
       </c>
       <c r="B40" s="25" t="inlineStr">
         <is>
-          <t>공구백화점(미산동)</t>
+          <t>맨날툴이야</t>
         </is>
       </c>
       <c r="C40" s="26" t="n">
+        <v>13</v>
+      </c>
+      <c r="D40" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="26" t="n">
+        <v>14</v>
+      </c>
+      <c r="F40" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="26" t="n">
         <v>16</v>
       </c>
-      <c r="D40" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="E40" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="F40" s="26" t="n">
-        <v>8</v>
-      </c>
-      <c r="G40" s="26" t="n">
-        <v>0</v>
-      </c>
       <c r="H40" s="26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I40" s="26" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J40" s="26" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="K40" s="26" t="n">
         <v>0</v>
@@ -2831,7 +2831,7 @@
         <v/>
       </c>
       <c r="P40" s="28">
-        <f>O40/O$73</f>
+        <f>O40/O$77</f>
         <v/>
       </c>
     </row>
@@ -2841,35 +2841,35 @@
       </c>
       <c r="B41" s="25" t="inlineStr">
         <is>
-          <t>예일공구상사</t>
+          <t>공구백화점(미산동)</t>
         </is>
       </c>
       <c r="C41" s="26" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D41" s="26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E41" s="26" t="n">
-        <v>57</v>
+        <v>5</v>
       </c>
       <c r="F41" s="26" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G41" s="26" t="n">
         <v>0</v>
       </c>
       <c r="H41" s="26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I41" s="26" t="n">
         <v>0</v>
       </c>
       <c r="J41" s="26" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K41" s="26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L41" s="26" t="n">
         <v>0</v>
@@ -2885,7 +2885,7 @@
         <v/>
       </c>
       <c r="P41" s="28">
-        <f>O41/O$73</f>
+        <f>O41/O$77</f>
         <v/>
       </c>
     </row>
@@ -2895,7 +2895,7 @@
       </c>
       <c r="B42" s="25" t="inlineStr">
         <is>
-          <t>하나테크</t>
+          <t>예일공구상사</t>
         </is>
       </c>
       <c r="C42" s="26" t="n">
@@ -2905,19 +2905,19 @@
         <v>0</v>
       </c>
       <c r="E42" s="26" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="F42" s="26" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="G42" s="26" t="n">
         <v>0</v>
       </c>
       <c r="H42" s="26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I42" s="26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J42" s="26" t="n">
         <v>0</v>
@@ -2939,7 +2939,7 @@
         <v/>
       </c>
       <c r="P42" s="28">
-        <f>O42/O$73</f>
+        <f>O42/O$77</f>
         <v/>
       </c>
     </row>
@@ -2977,7 +2977,7 @@
         <v>11</v>
       </c>
       <c r="K43" s="26" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L43" s="26" t="n">
         <v>0</v>
@@ -2993,7 +2993,7 @@
         <v/>
       </c>
       <c r="P43" s="28">
-        <f>O43/O$73</f>
+        <f>O43/O$77</f>
         <v/>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
         <v>0</v>
       </c>
       <c r="K44" s="26" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L44" s="26" t="n">
         <v>0</v>
@@ -3047,7 +3047,7 @@
         <v/>
       </c>
       <c r="P44" s="28">
-        <f>O44/O$73</f>
+        <f>O44/O$77</f>
         <v/>
       </c>
     </row>
@@ -3057,7 +3057,7 @@
       </c>
       <c r="B45" s="25" t="inlineStr">
         <is>
-          <t>인코테크 포승</t>
+          <t>신우툴스</t>
         </is>
       </c>
       <c r="C45" s="26" t="n">
@@ -3079,13 +3079,13 @@
         <v>0</v>
       </c>
       <c r="I45" s="26" t="n">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="J45" s="26" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K45" s="26" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="L45" s="26" t="n">
         <v>0</v>
@@ -3101,7 +3101,7 @@
         <v/>
       </c>
       <c r="P45" s="28">
-        <f>O45/O$73</f>
+        <f>O45/O$77</f>
         <v/>
       </c>
     </row>
@@ -3111,32 +3111,32 @@
       </c>
       <c r="B46" s="25" t="inlineStr">
         <is>
-          <t>유진상사(문래)</t>
+          <t>하나테크</t>
         </is>
       </c>
       <c r="C46" s="26" t="n">
         <v>0</v>
       </c>
       <c r="D46" s="26" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E46" s="26" t="n">
         <v>0</v>
       </c>
       <c r="F46" s="26" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="G46" s="26" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="H46" s="26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I46" s="26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J46" s="26" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K46" s="26" t="n">
         <v>0</v>
@@ -3155,7 +3155,7 @@
         <v/>
       </c>
       <c r="P46" s="28">
-        <f>O46/O$73</f>
+        <f>O46/O$77</f>
         <v/>
       </c>
     </row>
@@ -3165,29 +3165,29 @@
       </c>
       <c r="B47" s="25" t="inlineStr">
         <is>
-          <t>대명종합공구-코고툴(재연마)</t>
+          <t>인코테크 포승</t>
         </is>
       </c>
       <c r="C47" s="26" t="n">
         <v>0</v>
       </c>
       <c r="D47" s="26" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E47" s="26" t="n">
         <v>0</v>
       </c>
       <c r="F47" s="26" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G47" s="26" t="n">
         <v>0</v>
       </c>
       <c r="H47" s="26" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I47" s="26" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J47" s="26" t="n">
         <v>0</v>
@@ -3209,7 +3209,7 @@
         <v/>
       </c>
       <c r="P47" s="28">
-        <f>O47/O$73</f>
+        <f>O47/O$77</f>
         <v/>
       </c>
     </row>
@@ -3219,7 +3219,7 @@
       </c>
       <c r="B48" s="25" t="inlineStr">
         <is>
-          <t>신우툴스</t>
+          <t>코끼리공구</t>
         </is>
       </c>
       <c r="C48" s="26" t="n">
@@ -3235,19 +3235,19 @@
         <v>0</v>
       </c>
       <c r="G48" s="26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H48" s="26" t="n">
         <v>0</v>
       </c>
       <c r="I48" s="26" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J48" s="26" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K48" s="26" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="L48" s="26" t="n">
         <v>0</v>
@@ -3263,7 +3263,7 @@
         <v/>
       </c>
       <c r="P48" s="28">
-        <f>O48/O$73</f>
+        <f>O48/O$77</f>
         <v/>
       </c>
     </row>
@@ -3273,32 +3273,32 @@
       </c>
       <c r="B49" s="25" t="inlineStr">
         <is>
-          <t>영호종합공구(향남)</t>
+          <t>대명종합공구-코고툴(재연마)</t>
         </is>
       </c>
       <c r="C49" s="26" t="n">
         <v>0</v>
       </c>
       <c r="D49" s="26" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E49" s="26" t="n">
         <v>0</v>
       </c>
       <c r="F49" s="26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G49" s="26" t="n">
         <v>0</v>
       </c>
       <c r="H49" s="26" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="I49" s="26" t="n">
         <v>0</v>
       </c>
       <c r="J49" s="26" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K49" s="26" t="n">
         <v>0</v>
@@ -3317,7 +3317,7 @@
         <v/>
       </c>
       <c r="P49" s="28">
-        <f>O49/O$73</f>
+        <f>O49/O$77</f>
         <v/>
       </c>
     </row>
@@ -3327,7 +3327,7 @@
       </c>
       <c r="B50" s="25" t="inlineStr">
         <is>
-          <t>(주)코리아테크닉스</t>
+          <t>툴모아(시화)</t>
         </is>
       </c>
       <c r="C50" s="26" t="n">
@@ -3337,10 +3337,10 @@
         <v>0</v>
       </c>
       <c r="E50" s="26" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F50" s="26" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G50" s="26" t="n">
         <v>0</v>
@@ -3355,7 +3355,7 @@
         <v>0</v>
       </c>
       <c r="K50" s="26" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="L50" s="26" t="n">
         <v>0</v>
@@ -3371,7 +3371,7 @@
         <v/>
       </c>
       <c r="P50" s="28">
-        <f>O50/O$73</f>
+        <f>O50/O$77</f>
         <v/>
       </c>
     </row>
@@ -3381,7 +3381,7 @@
       </c>
       <c r="B51" s="25" t="inlineStr">
         <is>
-          <t>공구공구</t>
+          <t>영호종합공구(향남)</t>
         </is>
       </c>
       <c r="C51" s="26" t="n">
@@ -3397,16 +3397,16 @@
         <v>0</v>
       </c>
       <c r="G51" s="26" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H51" s="26" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I51" s="26" t="n">
         <v>0</v>
       </c>
       <c r="J51" s="26" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="K51" s="26" t="n">
         <v>0</v>
@@ -3425,7 +3425,7 @@
         <v/>
       </c>
       <c r="P51" s="28">
-        <f>O51/O$73</f>
+        <f>O51/O$77</f>
         <v/>
       </c>
     </row>
@@ -3435,29 +3435,29 @@
       </c>
       <c r="B52" s="25" t="inlineStr">
         <is>
-          <t>유성종합공구</t>
+          <t>(주)코리아테크닉스</t>
         </is>
       </c>
       <c r="C52" s="26" t="n">
         <v>0</v>
       </c>
       <c r="D52" s="26" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E52" s="26" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="F52" s="26" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G52" s="26" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H52" s="26" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I52" s="26" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J52" s="26" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
         <v/>
       </c>
       <c r="P52" s="28">
-        <f>O52/O$73</f>
+        <f>O52/O$77</f>
         <v/>
       </c>
     </row>
@@ -3489,7 +3489,7 @@
       </c>
       <c r="B53" s="25" t="inlineStr">
         <is>
-          <t>대양공구(인천)</t>
+          <t>공구공구</t>
         </is>
       </c>
       <c r="C53" s="26" t="n">
@@ -3502,10 +3502,10 @@
         <v>0</v>
       </c>
       <c r="F53" s="26" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G53" s="26" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H53" s="26" t="n">
         <v>0</v>
@@ -3514,7 +3514,7 @@
         <v>0</v>
       </c>
       <c r="J53" s="26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K53" s="26" t="n">
         <v>0</v>
@@ -3533,7 +3533,7 @@
         <v/>
       </c>
       <c r="P53" s="28">
-        <f>O53/O$73</f>
+        <f>O53/O$77</f>
         <v/>
       </c>
     </row>
@@ -3543,29 +3543,29 @@
       </c>
       <c r="B54" s="25" t="inlineStr">
         <is>
-          <t>코끼리공구</t>
+          <t>유성종합공구</t>
         </is>
       </c>
       <c r="C54" s="26" t="n">
         <v>0</v>
       </c>
       <c r="D54" s="26" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E54" s="26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F54" s="26" t="n">
         <v>0</v>
       </c>
       <c r="G54" s="26" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H54" s="26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I54" s="26" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="J54" s="26" t="n">
         <v>0</v>
@@ -3587,7 +3587,7 @@
         <v/>
       </c>
       <c r="P54" s="28">
-        <f>O54/O$73</f>
+        <f>O54/O$77</f>
         <v/>
       </c>
     </row>
@@ -3597,21 +3597,21 @@
       </c>
       <c r="B55" s="25" t="inlineStr">
         <is>
-          <t>(주)두영</t>
+          <t>대양공구(인천)</t>
         </is>
       </c>
       <c r="C55" s="26" t="n">
         <v>0</v>
       </c>
       <c r="D55" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" s="26" t="n">
         <v>14</v>
       </c>
-      <c r="E55" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F55" s="26" t="n">
-        <v>0</v>
-      </c>
       <c r="G55" s="26" t="n">
         <v>0</v>
       </c>
@@ -3622,7 +3622,7 @@
         <v>0</v>
       </c>
       <c r="J55" s="26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K55" s="26" t="n">
         <v>0</v>
@@ -3641,7 +3641,7 @@
         <v/>
       </c>
       <c r="P55" s="28">
-        <f>O55/O$73</f>
+        <f>O55/O$77</f>
         <v/>
       </c>
     </row>
@@ -3651,7 +3651,7 @@
       </c>
       <c r="B56" s="25" t="inlineStr">
         <is>
-          <t>N.T.S(엔티에스)-코고툴</t>
+          <t>세운상사</t>
         </is>
       </c>
       <c r="C56" s="26" t="n">
@@ -3664,22 +3664,22 @@
         <v>0</v>
       </c>
       <c r="F56" s="26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G56" s="26" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H56" s="26" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I56" s="26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J56" s="26" t="n">
         <v>0</v>
       </c>
       <c r="K56" s="26" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L56" s="26" t="n">
         <v>0</v>
@@ -3695,7 +3695,7 @@
         <v/>
       </c>
       <c r="P56" s="28">
-        <f>O56/O$73</f>
+        <f>O56/O$77</f>
         <v/>
       </c>
     </row>
@@ -3705,23 +3705,23 @@
       </c>
       <c r="B57" s="25" t="inlineStr">
         <is>
-          <t>(주)금천종합공구(독산)</t>
+          <t>(주)두영</t>
         </is>
       </c>
       <c r="C57" s="26" t="n">
         <v>0</v>
       </c>
       <c r="D57" s="26" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E57" s="26" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F57" s="26" t="n">
         <v>0</v>
       </c>
       <c r="G57" s="26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H57" s="26" t="n">
         <v>0</v>
@@ -3749,7 +3749,7 @@
         <v/>
       </c>
       <c r="P57" s="28">
-        <f>O57/O$73</f>
+        <f>O57/O$77</f>
         <v/>
       </c>
     </row>
@@ -3759,7 +3759,7 @@
       </c>
       <c r="B58" s="25" t="inlineStr">
         <is>
-          <t>세운상사</t>
+          <t>N.T.S(엔티에스)-코고툴</t>
         </is>
       </c>
       <c r="C58" s="26" t="n">
@@ -3772,16 +3772,16 @@
         <v>0</v>
       </c>
       <c r="F58" s="26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G58" s="26" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H58" s="26" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I58" s="26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J58" s="26" t="n">
         <v>0</v>
@@ -3803,7 +3803,7 @@
         <v/>
       </c>
       <c r="P58" s="28">
-        <f>O58/O$73</f>
+        <f>O58/O$77</f>
         <v/>
       </c>
     </row>
@@ -3813,7 +3813,7 @@
       </c>
       <c r="B59" s="25" t="inlineStr">
         <is>
-          <t>웰크리에이트-코고툴(재연마)</t>
+          <t>(주)금천종합공구(독산)</t>
         </is>
       </c>
       <c r="C59" s="26" t="n">
@@ -3823,13 +3823,13 @@
         <v>0</v>
       </c>
       <c r="E59" s="26" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F59" s="26" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G59" s="26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H59" s="26" t="n">
         <v>0</v>
@@ -3838,7 +3838,7 @@
         <v>0</v>
       </c>
       <c r="J59" s="26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K59" s="26" t="n">
         <v>0</v>
@@ -3857,7 +3857,7 @@
         <v/>
       </c>
       <c r="P59" s="28">
-        <f>O59/O$73</f>
+        <f>O59/O$77</f>
         <v/>
       </c>
     </row>
@@ -3867,32 +3867,32 @@
       </c>
       <c r="B60" s="25" t="inlineStr">
         <is>
-          <t>(주)성환공구</t>
+          <t>웰크리에이트-코고툴(재연마)</t>
         </is>
       </c>
       <c r="C60" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" s="26" t="n">
+        <v>10</v>
+      </c>
+      <c r="G60" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" s="26" t="n">
         <v>2</v>
-      </c>
-      <c r="D60" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E60" s="26" t="n">
-        <v>2</v>
-      </c>
-      <c r="F60" s="26" t="n">
-        <v>2</v>
-      </c>
-      <c r="G60" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H60" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" s="26" t="n">
-        <v>4</v>
       </c>
       <c r="K60" s="26" t="n">
         <v>0</v>
@@ -3911,7 +3911,7 @@
         <v/>
       </c>
       <c r="P60" s="28">
-        <f>O60/O$73</f>
+        <f>O60/O$77</f>
         <v/>
       </c>
     </row>
@@ -3921,20 +3921,20 @@
       </c>
       <c r="B61" s="25" t="inlineStr">
         <is>
-          <t>아시아툴링</t>
+          <t>(주)성환공구</t>
         </is>
       </c>
       <c r="C61" s="26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D61" s="26" t="n">
         <v>0</v>
       </c>
       <c r="E61" s="26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F61" s="26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G61" s="26" t="n">
         <v>0</v>
@@ -3946,7 +3946,7 @@
         <v>0</v>
       </c>
       <c r="J61" s="26" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="K61" s="26" t="n">
         <v>0</v>
@@ -3965,7 +3965,7 @@
         <v/>
       </c>
       <c r="P61" s="28">
-        <f>O61/O$73</f>
+        <f>O61/O$77</f>
         <v/>
       </c>
     </row>
@@ -3975,7 +3975,7 @@
       </c>
       <c r="B62" s="25" t="inlineStr">
         <is>
-          <t>동남종합상사(주)</t>
+          <t>아시아툴링</t>
         </is>
       </c>
       <c r="C62" s="26" t="n">
@@ -3997,10 +3997,10 @@
         <v>0</v>
       </c>
       <c r="I62" s="26" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J62" s="26" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K62" s="26" t="n">
         <v>0</v>
@@ -4019,7 +4019,7 @@
         <v/>
       </c>
       <c r="P62" s="28">
-        <f>O62/O$73</f>
+        <f>O62/O$77</f>
         <v/>
       </c>
     </row>
@@ -4029,7 +4029,7 @@
       </c>
       <c r="B63" s="25" t="inlineStr">
         <is>
-          <t>케이티툴스</t>
+          <t>동남종합상사(주)</t>
         </is>
       </c>
       <c r="C63" s="26" t="n">
@@ -4045,13 +4045,13 @@
         <v>0</v>
       </c>
       <c r="G63" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" s="26" t="n">
         <v>9</v>
-      </c>
-      <c r="H63" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I63" s="26" t="n">
-        <v>0</v>
       </c>
       <c r="J63" s="26" t="n">
         <v>0</v>
@@ -4073,7 +4073,7 @@
         <v/>
       </c>
       <c r="P63" s="28">
-        <f>O63/O$73</f>
+        <f>O63/O$77</f>
         <v/>
       </c>
     </row>
@@ -4083,14 +4083,14 @@
       </c>
       <c r="B64" s="25" t="inlineStr">
         <is>
-          <t>제이앤티</t>
+          <t>케이티툴스</t>
         </is>
       </c>
       <c r="C64" s="26" t="n">
         <v>0</v>
       </c>
       <c r="D64" s="26" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E64" s="26" t="n">
         <v>0</v>
@@ -4099,7 +4099,7 @@
         <v>0</v>
       </c>
       <c r="G64" s="26" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H64" s="26" t="n">
         <v>0</v>
@@ -4127,7 +4127,7 @@
         <v/>
       </c>
       <c r="P64" s="28">
-        <f>O64/O$73</f>
+        <f>O64/O$77</f>
         <v/>
       </c>
     </row>
@@ -4137,14 +4137,14 @@
       </c>
       <c r="B65" s="25" t="inlineStr">
         <is>
-          <t>금성툴테크</t>
+          <t>제이앤티</t>
         </is>
       </c>
       <c r="C65" s="26" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D65" s="26" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E65" s="26" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
         <v/>
       </c>
       <c r="P65" s="28">
-        <f>O65/O$73</f>
+        <f>O65/O$77</f>
         <v/>
       </c>
     </row>
@@ -4219,7 +4219,7 @@
         <v>1</v>
       </c>
       <c r="K66" s="26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L66" s="26" t="n">
         <v>0</v>
@@ -4235,7 +4235,7 @@
         <v/>
       </c>
       <c r="P66" s="28">
-        <f>O66/O$73</f>
+        <f>O66/O$77</f>
         <v/>
       </c>
     </row>
@@ -4245,11 +4245,11 @@
       </c>
       <c r="B67" s="25" t="inlineStr">
         <is>
-          <t>삼성패턴-코고툴(재연마)</t>
+          <t>금성툴테크</t>
         </is>
       </c>
       <c r="C67" s="26" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D67" s="26" t="n">
         <v>0</v>
@@ -4264,7 +4264,7 @@
         <v>0</v>
       </c>
       <c r="H67" s="26" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I67" s="26" t="n">
         <v>0</v>
@@ -4289,7 +4289,7 @@
         <v/>
       </c>
       <c r="P67" s="28">
-        <f>O67/O$73</f>
+        <f>O67/O$77</f>
         <v/>
       </c>
     </row>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="B68" s="25" t="inlineStr">
         <is>
-          <t>(아산)금영공구정공(주)</t>
+          <t>(주)성신툴링</t>
         </is>
       </c>
       <c r="C68" s="26" t="n">
@@ -4321,13 +4321,13 @@
         <v>0</v>
       </c>
       <c r="I68" s="26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J68" s="26" t="n">
         <v>0</v>
       </c>
       <c r="K68" s="26" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L68" s="26" t="n">
         <v>0</v>
@@ -4343,7 +4343,7 @@
         <v/>
       </c>
       <c r="P68" s="28">
-        <f>O68/O$73</f>
+        <f>O68/O$77</f>
         <v/>
       </c>
     </row>
@@ -4353,14 +4353,14 @@
       </c>
       <c r="B69" s="25" t="inlineStr">
         <is>
-          <t>(주)툴테크신화</t>
+          <t>삼성패턴-코고툴(재연마)</t>
         </is>
       </c>
       <c r="C69" s="26" t="n">
         <v>0</v>
       </c>
       <c r="D69" s="26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E69" s="26" t="n">
         <v>0</v>
@@ -4372,7 +4372,7 @@
         <v>0</v>
       </c>
       <c r="H69" s="26" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I69" s="26" t="n">
         <v>0</v>
@@ -4397,7 +4397,7 @@
         <v/>
       </c>
       <c r="P69" s="28">
-        <f>O69/O$73</f>
+        <f>O69/O$77</f>
         <v/>
       </c>
     </row>
@@ -4407,7 +4407,7 @@
       </c>
       <c r="B70" s="25" t="inlineStr">
         <is>
-          <t>엘엠툴스</t>
+          <t>(아산)금영공구정공(주)</t>
         </is>
       </c>
       <c r="C70" s="26" t="n">
@@ -4429,7 +4429,7 @@
         <v>0</v>
       </c>
       <c r="I70" s="26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J70" s="26" t="n">
         <v>0</v>
@@ -4451,7 +4451,7 @@
         <v/>
       </c>
       <c r="P70" s="28">
-        <f>O70/O$73</f>
+        <f>O70/O$77</f>
         <v/>
       </c>
     </row>
@@ -4461,17 +4461,17 @@
       </c>
       <c r="B71" s="25" t="inlineStr">
         <is>
-          <t>유성테크</t>
+          <t>(주)툴테크신화</t>
         </is>
       </c>
       <c r="C71" s="26" t="n">
         <v>0</v>
       </c>
       <c r="D71" s="26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E71" s="26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F71" s="26" t="n">
         <v>0</v>
@@ -4505,7 +4505,7 @@
         <v/>
       </c>
       <c r="P71" s="28">
-        <f>O71/O$73</f>
+        <f>O71/O$77</f>
         <v/>
       </c>
     </row>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="B72" s="25" t="inlineStr">
         <is>
-          <t>우주툴링</t>
+          <t>(주)삼진기공</t>
         </is>
       </c>
       <c r="C72" s="26" t="n">
@@ -4534,7 +4534,7 @@
         <v>0</v>
       </c>
       <c r="H72" s="26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I72" s="26" t="n">
         <v>0</v>
@@ -4543,7 +4543,7 @@
         <v>0</v>
       </c>
       <c r="K72" s="26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L72" s="26" t="n">
         <v>0</v>
@@ -4559,77 +4559,293 @@
         <v/>
       </c>
       <c r="P72" s="28">
-        <f>O72/O$73</f>
+        <f>O72/O$77</f>
         <v/>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="39" t="inlineStr">
+      <c r="A73" s="24" t="n">
+        <v>71</v>
+      </c>
+      <c r="B73" s="25" t="inlineStr">
+        <is>
+          <t>엘엠툴스</t>
+        </is>
+      </c>
+      <c r="C73" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="J73" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N73" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O73" s="27">
+        <f>SUM(C73:N73)</f>
+        <v/>
+      </c>
+      <c r="P73" s="28">
+        <f>O73/O$77</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="24" t="n">
+        <v>72</v>
+      </c>
+      <c r="B74" s="25" t="inlineStr">
+        <is>
+          <t>유성테크</t>
+        </is>
+      </c>
+      <c r="C74" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="F74" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N74" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O74" s="27">
+        <f>SUM(C74:N74)</f>
+        <v/>
+      </c>
+      <c r="P74" s="28">
+        <f>O74/O$77</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="24" t="n">
+        <v>73</v>
+      </c>
+      <c r="B75" s="25" t="inlineStr">
+        <is>
+          <t>정진툴링</t>
+        </is>
+      </c>
+      <c r="C75" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D75" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="L75" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N75" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" s="27">
+        <f>SUM(C75:N75)</f>
+        <v/>
+      </c>
+      <c r="P75" s="28">
+        <f>O75/O$77</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="24" t="n">
+        <v>74</v>
+      </c>
+      <c r="B76" s="25" t="inlineStr">
+        <is>
+          <t>우주툴링</t>
+        </is>
+      </c>
+      <c r="C76" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D76" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I76" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" s="27">
+        <f>SUM(C76:N76)</f>
+        <v/>
+      </c>
+      <c r="P76" s="28">
+        <f>O76/O$77</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="39" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
       </c>
-      <c r="B73" s="43" t="n"/>
-      <c r="C73" s="40">
-        <f>SUM(C3:C72)</f>
-        <v/>
-      </c>
-      <c r="D73" s="40">
-        <f>SUM(D3:D72)</f>
-        <v/>
-      </c>
-      <c r="E73" s="40">
-        <f>SUM(E3:E72)</f>
-        <v/>
-      </c>
-      <c r="F73" s="40">
-        <f>SUM(F3:F72)</f>
-        <v/>
-      </c>
-      <c r="G73" s="40">
-        <f>SUM(G3:G72)</f>
-        <v/>
-      </c>
-      <c r="H73" s="40">
-        <f>SUM(H3:H72)</f>
-        <v/>
-      </c>
-      <c r="I73" s="40">
-        <f>SUM(I3:I72)</f>
-        <v/>
-      </c>
-      <c r="J73" s="40">
-        <f>SUM(J3:J72)</f>
-        <v/>
-      </c>
-      <c r="K73" s="40">
-        <f>SUM(K3:K72)</f>
-        <v/>
-      </c>
-      <c r="L73" s="40">
-        <f>SUM(L3:L72)</f>
-        <v/>
-      </c>
-      <c r="M73" s="40">
-        <f>SUM(M3:M72)</f>
-        <v/>
-      </c>
-      <c r="N73" s="40">
-        <f>SUM(N3:N72)</f>
-        <v/>
-      </c>
-      <c r="O73" s="40">
-        <f>SUM(O3:O72)</f>
-        <v/>
-      </c>
-      <c r="P73" s="41" t="n">
+      <c r="B77" s="43" t="n"/>
+      <c r="C77" s="40">
+        <f>SUM(C3:C76)</f>
+        <v/>
+      </c>
+      <c r="D77" s="40">
+        <f>SUM(D3:D76)</f>
+        <v/>
+      </c>
+      <c r="E77" s="40">
+        <f>SUM(E3:E76)</f>
+        <v/>
+      </c>
+      <c r="F77" s="40">
+        <f>SUM(F3:F76)</f>
+        <v/>
+      </c>
+      <c r="G77" s="40">
+        <f>SUM(G3:G76)</f>
+        <v/>
+      </c>
+      <c r="H77" s="40">
+        <f>SUM(H3:H76)</f>
+        <v/>
+      </c>
+      <c r="I77" s="40">
+        <f>SUM(I3:I76)</f>
+        <v/>
+      </c>
+      <c r="J77" s="40">
+        <f>SUM(J3:J76)</f>
+        <v/>
+      </c>
+      <c r="K77" s="40">
+        <f>SUM(K3:K76)</f>
+        <v/>
+      </c>
+      <c r="L77" s="40">
+        <f>SUM(L3:L76)</f>
+        <v/>
+      </c>
+      <c r="M77" s="40">
+        <f>SUM(M3:M76)</f>
+        <v/>
+      </c>
+      <c r="N77" s="40">
+        <f>SUM(N3:N76)</f>
+        <v/>
+      </c>
+      <c r="O77" s="40">
+        <f>SUM(O3:O76)</f>
+        <v/>
+      </c>
+      <c r="P77" s="41" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:P1"/>
-    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="A77:B77"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4641,7 +4857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4652,55 +4868,764 @@
     <col width="13" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>2026년 9월 — 출하 데이터 없음</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+          <t>2026년 9월 출하현황 — 납품처별 출고량  (단위: 개)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="23" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="23" t="inlineStr">
         <is>
           <t>납품처명</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="23" t="inlineStr">
         <is>
           <t>9월 출고(개)</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="23" t="inlineStr">
         <is>
           <t>월간비율(%)</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="23" t="inlineStr">
         <is>
           <t>누적비율(%)</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="23" t="inlineStr">
         <is>
           <t>연간합계(개)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="22" t="inlineStr">
-        <is>
-          <t>해당 월 출하 데이터 없음</t>
-        </is>
+      <c r="A3" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="25" t="inlineStr">
+        <is>
+          <t>원영공구(구,원영상사)</t>
+        </is>
+      </c>
+      <c r="C3" s="27" t="n">
+        <v>257</v>
+      </c>
+      <c r="D3" s="28">
+        <f>C3/C$32</f>
+        <v/>
+      </c>
+      <c r="E3" s="28">
+        <f>D3</f>
+        <v/>
+      </c>
+      <c r="F3" s="27" t="n">
+        <v>1835</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="25" t="inlineStr">
+        <is>
+          <t>유진상사(문래)</t>
+        </is>
+      </c>
+      <c r="C4" s="27" t="n">
+        <v>195</v>
+      </c>
+      <c r="D4" s="28">
+        <f>C4/C$32</f>
+        <v/>
+      </c>
+      <c r="E4" s="28">
+        <f>E3+D4</f>
+        <v/>
+      </c>
+      <c r="F4" s="27" t="n">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="25" t="inlineStr">
+        <is>
+          <t>왕삼아공구</t>
+        </is>
+      </c>
+      <c r="C5" s="27" t="n">
+        <v>151</v>
+      </c>
+      <c r="D5" s="28">
+        <f>C5/C$32</f>
+        <v/>
+      </c>
+      <c r="E5" s="28">
+        <f>E4+D5</f>
+        <v/>
+      </c>
+      <c r="F5" s="27" t="n">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="25" t="inlineStr">
+        <is>
+          <t>아이티공구</t>
+        </is>
+      </c>
+      <c r="C6" s="27" t="n">
+        <v>127</v>
+      </c>
+      <c r="D6" s="28">
+        <f>C6/C$32</f>
+        <v/>
+      </c>
+      <c r="E6" s="28">
+        <f>E5+D6</f>
+        <v/>
+      </c>
+      <c r="F6" s="27" t="n">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="25" t="inlineStr">
+        <is>
+          <t>덕원종합상사</t>
+        </is>
+      </c>
+      <c r="C7" s="27" t="n">
+        <v>81</v>
+      </c>
+      <c r="D7" s="28">
+        <f>C7/C$32</f>
+        <v/>
+      </c>
+      <c r="E7" s="28">
+        <f>E6+D7</f>
+        <v/>
+      </c>
+      <c r="F7" s="27" t="n">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="35" t="inlineStr">
+        <is>
+          <t>영우툴링(창성툴)</t>
+        </is>
+      </c>
+      <c r="C8" s="37" t="n">
+        <v>79</v>
+      </c>
+      <c r="D8" s="38">
+        <f>C8/C$32</f>
+        <v/>
+      </c>
+      <c r="E8" s="38">
+        <f>E7+D8</f>
+        <v/>
+      </c>
+      <c r="F8" s="37" t="n">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="35" t="inlineStr">
+        <is>
+          <t>강민툴링(비봉)</t>
+        </is>
+      </c>
+      <c r="C9" s="37" t="n">
+        <v>78</v>
+      </c>
+      <c r="D9" s="38">
+        <f>C9/C$32</f>
+        <v/>
+      </c>
+      <c r="E9" s="38">
+        <f>E8+D9</f>
+        <v/>
+      </c>
+      <c r="F9" s="37" t="n">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="35" t="inlineStr">
+        <is>
+          <t>유비툴</t>
+        </is>
+      </c>
+      <c r="C10" s="37" t="n">
+        <v>52</v>
+      </c>
+      <c r="D10" s="38">
+        <f>C10/C$32</f>
+        <v/>
+      </c>
+      <c r="E10" s="38">
+        <f>E9+D10</f>
+        <v/>
+      </c>
+      <c r="F10" s="37" t="n">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="34" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="35" t="inlineStr">
+        <is>
+          <t>서림툴링</t>
+        </is>
+      </c>
+      <c r="C11" s="37" t="n">
+        <v>48</v>
+      </c>
+      <c r="D11" s="38">
+        <f>C11/C$32</f>
+        <v/>
+      </c>
+      <c r="E11" s="38">
+        <f>E10+D11</f>
+        <v/>
+      </c>
+      <c r="F11" s="37" t="n">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="34" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="35" t="inlineStr">
+        <is>
+          <t>신우툴링(남동)</t>
+        </is>
+      </c>
+      <c r="C12" s="37" t="n">
+        <v>44</v>
+      </c>
+      <c r="D12" s="38">
+        <f>C12/C$32</f>
+        <v/>
+      </c>
+      <c r="E12" s="38">
+        <f>E11+D12</f>
+        <v/>
+      </c>
+      <c r="F12" s="37" t="n">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="34" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="35" t="inlineStr">
+        <is>
+          <t>툴모아(시화)</t>
+        </is>
+      </c>
+      <c r="C13" s="37" t="n">
+        <v>36</v>
+      </c>
+      <c r="D13" s="38">
+        <f>C13/C$32</f>
+        <v/>
+      </c>
+      <c r="E13" s="38">
+        <f>E12+D13</f>
+        <v/>
+      </c>
+      <c r="F13" s="37" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="34" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="35" t="inlineStr">
+        <is>
+          <t>케이엠툴링</t>
+        </is>
+      </c>
+      <c r="C14" s="37" t="n">
+        <v>35</v>
+      </c>
+      <c r="D14" s="38">
+        <f>C14/C$32</f>
+        <v/>
+      </c>
+      <c r="E14" s="38">
+        <f>E13+D14</f>
+        <v/>
+      </c>
+      <c r="F14" s="37" t="n">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="34" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="35" t="inlineStr">
+        <is>
+          <t>영창툴링</t>
+        </is>
+      </c>
+      <c r="C15" s="37" t="n">
+        <v>25</v>
+      </c>
+      <c r="D15" s="38">
+        <f>C15/C$32</f>
+        <v/>
+      </c>
+      <c r="E15" s="38">
+        <f>E14+D15</f>
+        <v/>
+      </c>
+      <c r="F15" s="37" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="34" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="35" t="inlineStr">
+        <is>
+          <t>코끼리공구</t>
+        </is>
+      </c>
+      <c r="C16" s="37" t="n">
+        <v>23</v>
+      </c>
+      <c r="D16" s="38">
+        <f>C16/C$32</f>
+        <v/>
+      </c>
+      <c r="E16" s="38">
+        <f>E15+D16</f>
+        <v/>
+      </c>
+      <c r="F16" s="37" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="34" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="35" t="inlineStr">
+        <is>
+          <t>(주)일등정밀공구(안산)</t>
+        </is>
+      </c>
+      <c r="C17" s="37" t="n">
+        <v>22</v>
+      </c>
+      <c r="D17" s="38">
+        <f>C17/C$32</f>
+        <v/>
+      </c>
+      <c r="E17" s="38">
+        <f>E16+D17</f>
+        <v/>
+      </c>
+      <c r="F17" s="37" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="34" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="35" t="inlineStr">
+        <is>
+          <t>신우툴스</t>
+        </is>
+      </c>
+      <c r="C18" s="37" t="n">
+        <v>18</v>
+      </c>
+      <c r="D18" s="38">
+        <f>C18/C$32</f>
+        <v/>
+      </c>
+      <c r="E18" s="38">
+        <f>E17+D18</f>
+        <v/>
+      </c>
+      <c r="F18" s="37" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="34" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="35" t="inlineStr">
+        <is>
+          <t>반석공구</t>
+        </is>
+      </c>
+      <c r="C19" s="37" t="n">
+        <v>14</v>
+      </c>
+      <c r="D19" s="38">
+        <f>C19/C$32</f>
+        <v/>
+      </c>
+      <c r="E19" s="38">
+        <f>E18+D19</f>
+        <v/>
+      </c>
+      <c r="F19" s="37" t="n">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="34" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" s="35" t="inlineStr">
+        <is>
+          <t>(주)공화공구</t>
+        </is>
+      </c>
+      <c r="C20" s="37" t="n">
+        <v>11</v>
+      </c>
+      <c r="D20" s="38">
+        <f>C20/C$32</f>
+        <v/>
+      </c>
+      <c r="E20" s="38">
+        <f>E19+D20</f>
+        <v/>
+      </c>
+      <c r="F20" s="37" t="n">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="34" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="35" t="inlineStr">
+        <is>
+          <t>유성상공사</t>
+        </is>
+      </c>
+      <c r="C21" s="37" t="n">
+        <v>10</v>
+      </c>
+      <c r="D21" s="38">
+        <f>C21/C$32</f>
+        <v/>
+      </c>
+      <c r="E21" s="38">
+        <f>E20+D21</f>
+        <v/>
+      </c>
+      <c r="F21" s="37" t="n">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="34" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" s="35" t="inlineStr">
+        <is>
+          <t>(주)바로공구(정남)</t>
+        </is>
+      </c>
+      <c r="C22" s="37" t="n">
+        <v>10</v>
+      </c>
+      <c r="D22" s="38">
+        <f>C22/C$32</f>
+        <v/>
+      </c>
+      <c r="E22" s="38">
+        <f>E21+D22</f>
+        <v/>
+      </c>
+      <c r="F22" s="37" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="34" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" s="35" t="inlineStr">
+        <is>
+          <t>대성테크</t>
+        </is>
+      </c>
+      <c r="C23" s="37" t="n">
+        <v>9</v>
+      </c>
+      <c r="D23" s="38">
+        <f>C23/C$32</f>
+        <v/>
+      </c>
+      <c r="E23" s="38">
+        <f>E22+D23</f>
+        <v/>
+      </c>
+      <c r="F23" s="37" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="34" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" s="35" t="inlineStr">
+        <is>
+          <t>광진테크</t>
+        </is>
+      </c>
+      <c r="C24" s="37" t="n">
+        <v>7</v>
+      </c>
+      <c r="D24" s="38">
+        <f>C24/C$32</f>
+        <v/>
+      </c>
+      <c r="E24" s="38">
+        <f>E23+D24</f>
+        <v/>
+      </c>
+      <c r="F24" s="37" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="34" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" s="35" t="inlineStr">
+        <is>
+          <t>(주)성신툴링</t>
+        </is>
+      </c>
+      <c r="C25" s="37" t="n">
+        <v>7</v>
+      </c>
+      <c r="D25" s="38">
+        <f>C25/C$32</f>
+        <v/>
+      </c>
+      <c r="E25" s="38">
+        <f>E24+D25</f>
+        <v/>
+      </c>
+      <c r="F25" s="37" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="34" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" s="35" t="inlineStr">
+        <is>
+          <t>세운상사</t>
+        </is>
+      </c>
+      <c r="C26" s="37" t="n">
+        <v>6</v>
+      </c>
+      <c r="D26" s="38">
+        <f>C26/C$32</f>
+        <v/>
+      </c>
+      <c r="E26" s="38">
+        <f>E25+D26</f>
+        <v/>
+      </c>
+      <c r="F26" s="37" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="34" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" s="35" t="inlineStr">
+        <is>
+          <t>알제이코리아</t>
+        </is>
+      </c>
+      <c r="C27" s="37" t="n">
+        <v>5</v>
+      </c>
+      <c r="D27" s="38">
+        <f>C27/C$32</f>
+        <v/>
+      </c>
+      <c r="E27" s="38">
+        <f>E26+D27</f>
+        <v/>
+      </c>
+      <c r="F27" s="37" t="n">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="34" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" s="35" t="inlineStr">
+        <is>
+          <t>(주)삼진기공</t>
+        </is>
+      </c>
+      <c r="C28" s="37" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" s="38">
+        <f>C28/C$32</f>
+        <v/>
+      </c>
+      <c r="E28" s="38">
+        <f>E27+D28</f>
+        <v/>
+      </c>
+      <c r="F28" s="37" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="34" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" s="35" t="inlineStr">
+        <is>
+          <t>공구백화점(미산동)</t>
+        </is>
+      </c>
+      <c r="C29" s="37" t="n">
+        <v>2</v>
+      </c>
+      <c r="D29" s="38">
+        <f>C29/C$32</f>
+        <v/>
+      </c>
+      <c r="E29" s="38">
+        <f>E28+D29</f>
+        <v/>
+      </c>
+      <c r="F29" s="37" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="34" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" s="35" t="inlineStr">
+        <is>
+          <t>정진툴링</t>
+        </is>
+      </c>
+      <c r="C30" s="37" t="n">
+        <v>2</v>
+      </c>
+      <c r="D30" s="38">
+        <f>C30/C$32</f>
+        <v/>
+      </c>
+      <c r="E30" s="38">
+        <f>E29+D30</f>
+        <v/>
+      </c>
+      <c r="F30" s="37" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="34" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" s="35" t="inlineStr">
+        <is>
+          <t>대한초경공구</t>
+        </is>
+      </c>
+      <c r="C31" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" s="38">
+        <f>C31/C$32</f>
+        <v/>
+      </c>
+      <c r="E31" s="38">
+        <f>E30+D31</f>
+        <v/>
+      </c>
+      <c r="F31" s="37" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="39" t="inlineStr">
+        <is>
+          <t>합계</t>
+        </is>
+      </c>
+      <c r="B32" s="43" t="n"/>
+      <c r="C32" s="40">
+        <f>SUM(C3:C31)</f>
+        <v/>
+      </c>
+      <c r="D32" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" s="39" t="n"/>
+      <c r="F32" s="40">
+        <f>SUM(F3:F31)</f>
+        <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A32:B32"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5000,7 +5925,7 @@
         <v/>
       </c>
       <c r="F3" s="7" t="n">
-        <v>1578</v>
+        <v>1835</v>
       </c>
     </row>
     <row r="4">
@@ -5048,7 +5973,7 @@
         <v/>
       </c>
       <c r="F5" s="7" t="n">
-        <v>578</v>
+        <v>657</v>
       </c>
     </row>
     <row r="6">
@@ -5096,7 +6021,7 @@
         <v/>
       </c>
       <c r="F7" s="7" t="n">
-        <v>746</v>
+        <v>827</v>
       </c>
     </row>
     <row r="8">
@@ -5120,7 +6045,7 @@
         <v/>
       </c>
       <c r="F8" s="17" t="n">
-        <v>342</v>
+        <v>353</v>
       </c>
     </row>
     <row r="9">
@@ -5144,7 +6069,7 @@
         <v/>
       </c>
       <c r="F9" s="17" t="n">
-        <v>310</v>
+        <v>315</v>
       </c>
     </row>
     <row r="10">
@@ -5168,7 +6093,7 @@
         <v/>
       </c>
       <c r="F10" s="17" t="n">
-        <v>554</v>
+        <v>681</v>
       </c>
     </row>
     <row r="11">
@@ -5216,7 +6141,7 @@
         <v/>
       </c>
       <c r="F12" s="17" t="n">
-        <v>119</v>
+        <v>144</v>
       </c>
     </row>
     <row r="13">
@@ -5264,7 +6189,7 @@
         <v/>
       </c>
       <c r="F14" s="17" t="n">
-        <v>388</v>
+        <v>440</v>
       </c>
     </row>
     <row r="15">
@@ -5288,7 +6213,7 @@
         <v/>
       </c>
       <c r="F15" s="17" t="n">
-        <v>73</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -5312,7 +6237,7 @@
         <v/>
       </c>
       <c r="F16" s="17" t="n">
-        <v>307</v>
+        <v>321</v>
       </c>
     </row>
     <row r="17">
@@ -5336,7 +6261,7 @@
         <v/>
       </c>
       <c r="F17" s="17" t="n">
-        <v>197</v>
+        <v>232</v>
       </c>
     </row>
     <row r="18">
@@ -5360,7 +6285,7 @@
         <v/>
       </c>
       <c r="F18" s="17" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19">
@@ -5408,7 +6333,7 @@
         <v/>
       </c>
       <c r="F20" s="17" t="n">
-        <v>294</v>
+        <v>445</v>
       </c>
     </row>
     <row r="21">
@@ -5432,7 +6357,7 @@
         <v/>
       </c>
       <c r="F21" s="17" t="n">
-        <v>953</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="22">
@@ -5480,7 +6405,7 @@
         <v/>
       </c>
       <c r="F23" s="17" t="n">
-        <v>171</v>
+        <v>219</v>
       </c>
     </row>
     <row r="24">
@@ -5528,7 +6453,7 @@
         <v/>
       </c>
       <c r="F25" s="17" t="n">
-        <v>97</v>
+        <v>107</v>
       </c>
     </row>
     <row r="26">
@@ -5733,7 +6658,7 @@
         <v/>
       </c>
       <c r="F5" s="7" t="n">
-        <v>953</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="6">
@@ -5781,7 +6706,7 @@
         <v/>
       </c>
       <c r="F7" s="7" t="n">
-        <v>746</v>
+        <v>827</v>
       </c>
     </row>
     <row r="8">
@@ -5829,7 +6754,7 @@
         <v/>
       </c>
       <c r="F9" s="17" t="n">
-        <v>554</v>
+        <v>681</v>
       </c>
     </row>
     <row r="10">
@@ -5877,7 +6802,7 @@
         <v/>
       </c>
       <c r="F11" s="17" t="n">
-        <v>578</v>
+        <v>657</v>
       </c>
     </row>
     <row r="12">
@@ -5901,7 +6826,7 @@
         <v/>
       </c>
       <c r="F12" s="17" t="n">
-        <v>1578</v>
+        <v>1835</v>
       </c>
     </row>
     <row r="13">
@@ -5949,7 +6874,7 @@
         <v/>
       </c>
       <c r="F14" s="17" t="n">
-        <v>342</v>
+        <v>353</v>
       </c>
     </row>
     <row r="15">
@@ -5997,7 +6922,7 @@
         <v/>
       </c>
       <c r="F16" s="17" t="n">
-        <v>171</v>
+        <v>219</v>
       </c>
     </row>
     <row r="17">
@@ -6021,7 +6946,7 @@
         <v/>
       </c>
       <c r="F17" s="17" t="n">
-        <v>388</v>
+        <v>440</v>
       </c>
     </row>
     <row r="18">
@@ -6045,7 +6970,7 @@
         <v/>
       </c>
       <c r="F18" s="17" t="n">
-        <v>307</v>
+        <v>321</v>
       </c>
     </row>
     <row r="19">
@@ -6069,7 +6994,7 @@
         <v/>
       </c>
       <c r="F19" s="17" t="n">
-        <v>294</v>
+        <v>445</v>
       </c>
     </row>
     <row r="20">
@@ -6117,7 +7042,7 @@
         <v/>
       </c>
       <c r="F21" s="17" t="n">
-        <v>66</v>
+        <v>88</v>
       </c>
     </row>
     <row r="22">
@@ -6165,7 +7090,7 @@
         <v/>
       </c>
       <c r="F23" s="17" t="n">
-        <v>119</v>
+        <v>144</v>
       </c>
     </row>
     <row r="24">
@@ -6237,7 +7162,7 @@
         <v/>
       </c>
       <c r="F26" s="17" t="n">
-        <v>38</v>
+        <v>233</v>
       </c>
     </row>
     <row r="27">
@@ -6357,7 +7282,7 @@
         <v/>
       </c>
       <c r="F31" s="17" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="32">
@@ -6381,7 +7306,7 @@
         <v/>
       </c>
       <c r="F32" s="17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33">
@@ -6490,7 +7415,7 @@
         <v/>
       </c>
       <c r="F3" s="7" t="n">
-        <v>953</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="4">
@@ -6586,7 +7511,7 @@
         <v/>
       </c>
       <c r="F7" s="7" t="n">
-        <v>1578</v>
+        <v>1835</v>
       </c>
     </row>
     <row r="8">
@@ -6682,7 +7607,7 @@
         <v/>
       </c>
       <c r="F11" s="17" t="n">
-        <v>746</v>
+        <v>827</v>
       </c>
     </row>
     <row r="12">
@@ -6706,7 +7631,7 @@
         <v/>
       </c>
       <c r="F12" s="17" t="n">
-        <v>310</v>
+        <v>315</v>
       </c>
     </row>
     <row r="13">
@@ -6754,7 +7679,7 @@
         <v/>
       </c>
       <c r="F14" s="17" t="n">
-        <v>388</v>
+        <v>440</v>
       </c>
     </row>
     <row r="15">
@@ -6778,7 +7703,7 @@
         <v/>
       </c>
       <c r="F15" s="17" t="n">
-        <v>554</v>
+        <v>681</v>
       </c>
     </row>
     <row r="16">
@@ -6802,7 +7727,7 @@
         <v/>
       </c>
       <c r="F16" s="17" t="n">
-        <v>578</v>
+        <v>657</v>
       </c>
     </row>
     <row r="17">
@@ -6826,7 +7751,7 @@
         <v/>
       </c>
       <c r="F17" s="17" t="n">
-        <v>325</v>
+        <v>369</v>
       </c>
     </row>
     <row r="18">
@@ -6874,7 +7799,7 @@
         <v/>
       </c>
       <c r="F19" s="17" t="n">
-        <v>307</v>
+        <v>321</v>
       </c>
     </row>
     <row r="20">
@@ -6898,7 +7823,7 @@
         <v/>
       </c>
       <c r="F20" s="17" t="n">
-        <v>197</v>
+        <v>232</v>
       </c>
     </row>
     <row r="21">
@@ -6922,7 +7847,7 @@
         <v/>
       </c>
       <c r="F21" s="17" t="n">
-        <v>171</v>
+        <v>219</v>
       </c>
     </row>
     <row r="22">
@@ -6970,7 +7895,7 @@
         <v/>
       </c>
       <c r="F23" s="17" t="n">
-        <v>119</v>
+        <v>144</v>
       </c>
     </row>
     <row r="24">
@@ -7042,7 +7967,7 @@
         <v/>
       </c>
       <c r="F26" s="17" t="n">
-        <v>342</v>
+        <v>353</v>
       </c>
     </row>
     <row r="27">
@@ -7090,7 +8015,7 @@
         <v/>
       </c>
       <c r="F28" s="17" t="n">
-        <v>73</v>
+        <v>80</v>
       </c>
     </row>
     <row r="29">
@@ -7138,7 +8063,7 @@
         <v/>
       </c>
       <c r="F30" s="17" t="n">
-        <v>42</v>
+        <v>52</v>
       </c>
     </row>
     <row r="31">
@@ -7162,7 +8087,7 @@
         <v/>
       </c>
       <c r="F31" s="17" t="n">
-        <v>97</v>
+        <v>107</v>
       </c>
     </row>
     <row r="32">
@@ -7186,7 +8111,7 @@
         <v/>
       </c>
       <c r="F32" s="17" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="33">
@@ -7439,7 +8364,7 @@
         <v/>
       </c>
       <c r="F6" s="7" t="n">
-        <v>953</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="7">
@@ -7463,7 +8388,7 @@
         <v/>
       </c>
       <c r="F7" s="7" t="n">
-        <v>1578</v>
+        <v>1835</v>
       </c>
     </row>
     <row r="8">
@@ -7487,7 +8412,7 @@
         <v/>
       </c>
       <c r="F8" s="17" t="n">
-        <v>746</v>
+        <v>827</v>
       </c>
     </row>
     <row r="9">
@@ -7511,7 +8436,7 @@
         <v/>
       </c>
       <c r="F9" s="17" t="n">
-        <v>310</v>
+        <v>315</v>
       </c>
     </row>
     <row r="10">
@@ -7559,7 +8484,7 @@
         <v/>
       </c>
       <c r="F11" s="17" t="n">
-        <v>388</v>
+        <v>440</v>
       </c>
     </row>
     <row r="12">
@@ -7583,7 +8508,7 @@
         <v/>
       </c>
       <c r="F12" s="17" t="n">
-        <v>554</v>
+        <v>681</v>
       </c>
     </row>
     <row r="13">
@@ -7607,7 +8532,7 @@
         <v/>
       </c>
       <c r="F13" s="17" t="n">
-        <v>578</v>
+        <v>657</v>
       </c>
     </row>
     <row r="14">
@@ -7631,7 +8556,7 @@
         <v/>
       </c>
       <c r="F14" s="17" t="n">
-        <v>294</v>
+        <v>445</v>
       </c>
     </row>
     <row r="15">
@@ -7655,7 +8580,7 @@
         <v/>
       </c>
       <c r="F15" s="17" t="n">
-        <v>197</v>
+        <v>232</v>
       </c>
     </row>
     <row r="16">
@@ -7703,7 +8628,7 @@
         <v/>
       </c>
       <c r="F17" s="17" t="n">
-        <v>171</v>
+        <v>219</v>
       </c>
     </row>
     <row r="18">
@@ -7727,7 +8652,7 @@
         <v/>
       </c>
       <c r="F18" s="17" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19">
@@ -7751,7 +8676,7 @@
         <v/>
       </c>
       <c r="F19" s="17" t="n">
-        <v>119</v>
+        <v>144</v>
       </c>
     </row>
     <row r="20">
@@ -7823,7 +8748,7 @@
         <v/>
       </c>
       <c r="F22" s="17" t="n">
-        <v>73</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23">
@@ -7847,7 +8772,7 @@
         <v/>
       </c>
       <c r="F23" s="17" t="n">
-        <v>307</v>
+        <v>321</v>
       </c>
     </row>
     <row r="24">
@@ -7895,7 +8820,7 @@
         <v/>
       </c>
       <c r="F25" s="17" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="26">
@@ -7991,7 +8916,7 @@
         <v/>
       </c>
       <c r="F29" s="17" t="n">
-        <v>97</v>
+        <v>107</v>
       </c>
     </row>
     <row r="30">
@@ -8015,7 +8940,7 @@
         <v/>
       </c>
       <c r="F30" s="17" t="n">
-        <v>342</v>
+        <v>353</v>
       </c>
     </row>
     <row r="31">
@@ -8063,7 +8988,7 @@
         <v/>
       </c>
       <c r="F32" s="17" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="33">
@@ -8220,7 +9145,7 @@
         <v/>
       </c>
       <c r="F5" s="7" t="n">
-        <v>325</v>
+        <v>369</v>
       </c>
     </row>
     <row r="6">
@@ -8244,7 +9169,7 @@
         <v/>
       </c>
       <c r="F6" s="7" t="n">
-        <v>388</v>
+        <v>440</v>
       </c>
     </row>
     <row r="7">
@@ -8292,7 +9217,7 @@
         <v/>
       </c>
       <c r="F8" s="17" t="n">
-        <v>294</v>
+        <v>445</v>
       </c>
     </row>
     <row r="9">
@@ -8340,7 +9265,7 @@
         <v/>
       </c>
       <c r="F10" s="17" t="n">
-        <v>554</v>
+        <v>681</v>
       </c>
     </row>
     <row r="11">
@@ -8364,7 +9289,7 @@
         <v/>
       </c>
       <c r="F11" s="17" t="n">
-        <v>953</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="12">
@@ -8388,7 +9313,7 @@
         <v/>
       </c>
       <c r="F12" s="17" t="n">
-        <v>307</v>
+        <v>321</v>
       </c>
     </row>
     <row r="13">
@@ -8412,7 +9337,7 @@
         <v/>
       </c>
       <c r="F13" s="17" t="n">
-        <v>1578</v>
+        <v>1835</v>
       </c>
     </row>
     <row r="14">
@@ -8436,7 +9361,7 @@
         <v/>
       </c>
       <c r="F14" s="17" t="n">
-        <v>578</v>
+        <v>657</v>
       </c>
     </row>
     <row r="15">
@@ -8484,7 +9409,7 @@
         <v/>
       </c>
       <c r="F16" s="17" t="n">
-        <v>746</v>
+        <v>827</v>
       </c>
     </row>
     <row r="17">
@@ -8532,7 +9457,7 @@
         <v/>
       </c>
       <c r="F18" s="17" t="n">
-        <v>66</v>
+        <v>88</v>
       </c>
     </row>
     <row r="19">
@@ -8556,7 +9481,7 @@
         <v/>
       </c>
       <c r="F19" s="17" t="n">
-        <v>342</v>
+        <v>353</v>
       </c>
     </row>
     <row r="20">
@@ -8604,7 +9529,7 @@
         <v/>
       </c>
       <c r="F21" s="17" t="n">
-        <v>119</v>
+        <v>144</v>
       </c>
     </row>
     <row r="22">
@@ -8652,7 +9577,7 @@
         <v/>
       </c>
       <c r="F23" s="17" t="n">
-        <v>197</v>
+        <v>232</v>
       </c>
     </row>
     <row r="24">
@@ -8700,7 +9625,7 @@
         <v/>
       </c>
       <c r="F25" s="17" t="n">
-        <v>38</v>
+        <v>233</v>
       </c>
     </row>
     <row r="26">
@@ -8796,7 +9721,7 @@
         <v/>
       </c>
       <c r="F29" s="17" t="n">
-        <v>310</v>
+        <v>315</v>
       </c>
     </row>
     <row r="30">
@@ -8868,7 +9793,7 @@
         <v/>
       </c>
       <c r="F32" s="17" t="n">
-        <v>16</v>
+        <v>39</v>
       </c>
     </row>
     <row r="33">
@@ -8916,7 +9841,7 @@
         <v/>
       </c>
       <c r="F34" s="17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35">
@@ -9073,7 +9998,7 @@
         <v/>
       </c>
       <c r="F5" s="27" t="n">
-        <v>953</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="6">
@@ -9121,7 +10046,7 @@
         <v/>
       </c>
       <c r="F7" s="27" t="n">
-        <v>1578</v>
+        <v>1835</v>
       </c>
     </row>
     <row r="8">
@@ -9217,7 +10142,7 @@
         <v/>
       </c>
       <c r="F11" s="37" t="n">
-        <v>97</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12">
@@ -9241,7 +10166,7 @@
         <v/>
       </c>
       <c r="F12" s="37" t="n">
-        <v>746</v>
+        <v>827</v>
       </c>
     </row>
     <row r="13">
@@ -9265,7 +10190,7 @@
         <v/>
       </c>
       <c r="F13" s="37" t="n">
-        <v>310</v>
+        <v>315</v>
       </c>
     </row>
     <row r="14">
@@ -9289,7 +10214,7 @@
         <v/>
       </c>
       <c r="F14" s="37" t="n">
-        <v>578</v>
+        <v>657</v>
       </c>
     </row>
     <row r="15">
@@ -9313,7 +10238,7 @@
         <v/>
       </c>
       <c r="F15" s="37" t="n">
-        <v>307</v>
+        <v>321</v>
       </c>
     </row>
     <row r="16">
@@ -9337,7 +10262,7 @@
         <v/>
       </c>
       <c r="F16" s="37" t="n">
-        <v>294</v>
+        <v>445</v>
       </c>
     </row>
     <row r="17">
@@ -9409,7 +10334,7 @@
         <v/>
       </c>
       <c r="F19" s="37" t="n">
-        <v>325</v>
+        <v>369</v>
       </c>
     </row>
     <row r="20">
@@ -9457,7 +10382,7 @@
         <v/>
       </c>
       <c r="F21" s="37" t="n">
-        <v>171</v>
+        <v>219</v>
       </c>
     </row>
     <row r="22">
@@ -9529,7 +10454,7 @@
         <v/>
       </c>
       <c r="F24" s="37" t="n">
-        <v>388</v>
+        <v>440</v>
       </c>
     </row>
     <row r="25">
@@ -9553,7 +10478,7 @@
         <v/>
       </c>
       <c r="F25" s="37" t="n">
-        <v>342</v>
+        <v>353</v>
       </c>
     </row>
     <row r="26">
@@ -9577,7 +10502,7 @@
         <v/>
       </c>
       <c r="F26" s="37" t="n">
-        <v>554</v>
+        <v>681</v>
       </c>
     </row>
     <row r="27">
@@ -9601,7 +10526,7 @@
         <v/>
       </c>
       <c r="F27" s="37" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
     </row>
     <row r="28">
@@ -9625,7 +10550,7 @@
         <v/>
       </c>
       <c r="F28" s="37" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="29">
@@ -9649,7 +10574,7 @@
         <v/>
       </c>
       <c r="F29" s="37" t="n">
-        <v>119</v>
+        <v>144</v>
       </c>
     </row>
     <row r="30">
@@ -9673,7 +10598,7 @@
         <v/>
       </c>
       <c r="F30" s="37" t="n">
-        <v>73</v>
+        <v>80</v>
       </c>
     </row>
     <row r="31">
@@ -9721,7 +10646,7 @@
         <v/>
       </c>
       <c r="F32" s="37" t="n">
-        <v>66</v>
+        <v>88</v>
       </c>
     </row>
     <row r="33">
@@ -9793,7 +10718,7 @@
         <v/>
       </c>
       <c r="F35" s="37" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="36">
@@ -9865,7 +10790,7 @@
         <v/>
       </c>
       <c r="F38" s="37" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39">
@@ -10022,7 +10947,7 @@
         <v/>
       </c>
       <c r="F3" s="27" t="n">
-        <v>1578</v>
+        <v>1835</v>
       </c>
     </row>
     <row r="4">
@@ -10166,7 +11091,7 @@
         <v/>
       </c>
       <c r="F9" s="37" t="n">
-        <v>554</v>
+        <v>681</v>
       </c>
     </row>
     <row r="10">
@@ -10190,7 +11115,7 @@
         <v/>
       </c>
       <c r="F10" s="37" t="n">
-        <v>746</v>
+        <v>827</v>
       </c>
     </row>
     <row r="11">
@@ -10214,7 +11139,7 @@
         <v/>
       </c>
       <c r="F11" s="37" t="n">
-        <v>578</v>
+        <v>657</v>
       </c>
     </row>
     <row r="12">
@@ -10238,7 +11163,7 @@
         <v/>
       </c>
       <c r="F12" s="37" t="n">
-        <v>342</v>
+        <v>353</v>
       </c>
     </row>
     <row r="13">
@@ -10262,7 +11187,7 @@
         <v/>
       </c>
       <c r="F13" s="37" t="n">
-        <v>197</v>
+        <v>232</v>
       </c>
     </row>
     <row r="14">
@@ -10310,7 +11235,7 @@
         <v/>
       </c>
       <c r="F15" s="37" t="n">
-        <v>310</v>
+        <v>315</v>
       </c>
     </row>
     <row r="16">
@@ -10334,7 +11259,7 @@
         <v/>
       </c>
       <c r="F16" s="37" t="n">
-        <v>953</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="17">
@@ -10358,7 +11283,7 @@
         <v/>
       </c>
       <c r="F17" s="37" t="n">
-        <v>171</v>
+        <v>219</v>
       </c>
     </row>
     <row r="18">
@@ -10382,7 +11307,7 @@
         <v/>
       </c>
       <c r="F18" s="37" t="n">
-        <v>42</v>
+        <v>52</v>
       </c>
     </row>
     <row r="19">
@@ -10406,7 +11331,7 @@
         <v/>
       </c>
       <c r="F19" s="37" t="n">
-        <v>388</v>
+        <v>440</v>
       </c>
     </row>
     <row r="20">
@@ -10430,7 +11355,7 @@
         <v/>
       </c>
       <c r="F20" s="37" t="n">
-        <v>294</v>
+        <v>445</v>
       </c>
     </row>
     <row r="21">
@@ -10454,7 +11379,7 @@
         <v/>
       </c>
       <c r="F21" s="37" t="n">
-        <v>16</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22">
@@ -10478,7 +11403,7 @@
         <v/>
       </c>
       <c r="F22" s="37" t="n">
-        <v>307</v>
+        <v>321</v>
       </c>
     </row>
     <row r="23">
@@ -10502,7 +11427,7 @@
         <v/>
       </c>
       <c r="F23" s="37" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24">
@@ -10742,7 +11667,7 @@
         <v/>
       </c>
       <c r="F33" s="37" t="n">
-        <v>97</v>
+        <v>107</v>
       </c>
     </row>
     <row r="34">
@@ -10790,7 +11715,7 @@
         <v/>
       </c>
       <c r="F35" s="37" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36">
@@ -10838,7 +11763,7 @@
         <v/>
       </c>
       <c r="F37" s="37" t="n">
-        <v>38</v>
+        <v>233</v>
       </c>
     </row>
     <row r="38">
@@ -10995,7 +11920,7 @@
         <v/>
       </c>
       <c r="F5" s="27" t="n">
-        <v>746</v>
+        <v>827</v>
       </c>
     </row>
     <row r="6">
@@ -11019,7 +11944,7 @@
         <v/>
       </c>
       <c r="F6" s="27" t="n">
-        <v>1578</v>
+        <v>1835</v>
       </c>
     </row>
     <row r="7">
@@ -11091,7 +12016,7 @@
         <v/>
       </c>
       <c r="F9" s="27" t="n">
-        <v>342</v>
+        <v>353</v>
       </c>
     </row>
     <row r="10">
@@ -11115,7 +12040,7 @@
         <v/>
       </c>
       <c r="F10" s="27" t="n">
-        <v>325</v>
+        <v>369</v>
       </c>
     </row>
     <row r="11">
@@ -11139,7 +12064,7 @@
         <v/>
       </c>
       <c r="F11" s="27" t="n">
-        <v>554</v>
+        <v>681</v>
       </c>
     </row>
     <row r="12">
@@ -11163,7 +12088,7 @@
         <v/>
       </c>
       <c r="F12" s="27" t="n">
-        <v>307</v>
+        <v>321</v>
       </c>
     </row>
     <row r="13">
@@ -11211,7 +12136,7 @@
         <v/>
       </c>
       <c r="F14" s="27" t="n">
-        <v>578</v>
+        <v>657</v>
       </c>
     </row>
     <row r="15">
@@ -11259,7 +12184,7 @@
         <v/>
       </c>
       <c r="F16" s="27" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -11355,7 +12280,7 @@
         <v/>
       </c>
       <c r="F20" s="27" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21">
@@ -11379,7 +12304,7 @@
         <v/>
       </c>
       <c r="F21" s="27" t="n">
-        <v>171</v>
+        <v>219</v>
       </c>
     </row>
     <row r="22">
@@ -11403,7 +12328,7 @@
         <v/>
       </c>
       <c r="F22" s="27" t="n">
-        <v>953</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="23">
@@ -11475,7 +12400,7 @@
         <v/>
       </c>
       <c r="F25" s="27" t="n">
-        <v>42</v>
+        <v>52</v>
       </c>
     </row>
     <row r="26">
@@ -11499,7 +12424,7 @@
         <v/>
       </c>
       <c r="F26" s="27" t="n">
-        <v>38</v>
+        <v>233</v>
       </c>
     </row>
     <row r="27">
@@ -11571,7 +12496,7 @@
         <v/>
       </c>
       <c r="F29" s="27" t="n">
-        <v>73</v>
+        <v>80</v>
       </c>
     </row>
     <row r="30">
@@ -11595,7 +12520,7 @@
         <v/>
       </c>
       <c r="F30" s="27" t="n">
-        <v>97</v>
+        <v>107</v>
       </c>
     </row>
     <row r="31">
@@ -11715,7 +12640,7 @@
         <v/>
       </c>
       <c r="F35" s="27" t="n">
-        <v>66</v>
+        <v>88</v>
       </c>
     </row>
     <row r="36">
@@ -11739,7 +12664,7 @@
         <v/>
       </c>
       <c r="F36" s="27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37">
@@ -11763,7 +12688,7 @@
         <v/>
       </c>
       <c r="F37" s="27" t="n">
-        <v>294</v>
+        <v>445</v>
       </c>
     </row>
     <row r="38">
